--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -1619,7 +1619,7 @@
         <v>136483159</v>
       </c>
       <c r="B11" t="n">
-        <v>101450</v>
+        <v>101453</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -1619,7 +1619,7 @@
         <v>136483159</v>
       </c>
       <c r="B11" t="n">
-        <v>101453</v>
+        <v>101454</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist, Sofia Åström</t>
+          <t>Sofia Åström, Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Sofia Åström, Rasmus Häggqvist</t>
+          <t>Rasmus Häggqvist, Sofia Åström</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -1619,7 +1619,7 @@
         <v>136483159</v>
       </c>
       <c r="B11" t="n">
-        <v>101454</v>
+        <v>101459</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rasmus Häggqvist, Sofia Åström</t>
+          <t>Sofia Åström, Rasmus Häggqvist</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ142"/>
+  <dimension ref="A1:AZ147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1619,7 +1619,7 @@
         <v>136483159</v>
       </c>
       <c r="B11" t="n">
-        <v>101459</v>
+        <v>101461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5339,48 +5339,48 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>124427365</v>
+        <v>136866951</v>
       </c>
       <c r="B47" t="n">
-        <v>79946</v>
+        <v>79476</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>854939</v>
+        <v>855186</v>
       </c>
       <c r="R47" t="n">
-        <v>7478324</v>
+        <v>7477941</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5404,12 +5404,12 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5435,54 +5435,54 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427365</t>
+          <t>https://artportalen.se/Sighting/136866951</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123699044</v>
+        <v>124427365</v>
       </c>
       <c r="B48" t="n">
-        <v>80336</v>
+        <v>79946</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6456</v>
+        <v>6453</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>854836</v>
+        <v>854939</v>
       </c>
       <c r="R48" t="n">
-        <v>7478088</v>
+        <v>7478324</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5506,17 +5506,12 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På  grov asp, 180 cm i omkrets.</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5525,7 +5520,6 @@
       <c r="AE48" t="b">
         <v>0</v>
       </c>
-      <c r="AF48" t="inlineStr"/>
       <c r="AG48" t="b">
         <v>0</v>
       </c>
@@ -5543,13 +5537,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123699044</t>
+          <t>https://artportalen.se/Sighting/124427365</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123699045</v>
+        <v>123699044</v>
       </c>
       <c r="B49" t="n">
         <v>80336</v>
@@ -5584,10 +5578,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>855058</v>
+        <v>854836</v>
       </c>
       <c r="R49" t="n">
-        <v>7478025</v>
+        <v>7478088</v>
       </c>
       <c r="S49" t="n">
         <v>15</v>
@@ -5622,12 +5616,18 @@
           <t>2025-04-01</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På  grov asp, 180 cm i omkrets.</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
       <c r="AE49" t="b">
         <v>0</v>
       </c>
+      <c r="AF49" t="inlineStr"/>
       <c r="AG49" t="b">
         <v>0</v>
       </c>
@@ -5645,13 +5645,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123699045</t>
+          <t>https://artportalen.se/Sighting/123699044</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123699046</v>
+        <v>123699045</v>
       </c>
       <c r="B50" t="n">
         <v>80336</v>
@@ -5686,10 +5686,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>855119</v>
+        <v>855058</v>
       </c>
       <c r="R50" t="n">
-        <v>7478027</v>
+        <v>7478025</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5747,16 +5747,16 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123699046</t>
+          <t>https://artportalen.se/Sighting/123699045</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123699082</v>
+        <v>123699046</v>
       </c>
       <c r="B51" t="n">
-        <v>80367</v>
+        <v>80336</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5764,21 +5764,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6457</v>
+        <v>6456</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dvärgtufs</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Scytinium teretiusculum</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Wallr.) Otálora et al.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5788,10 +5788,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>855140</v>
+        <v>855119</v>
       </c>
       <c r="R51" t="n">
-        <v>7478068</v>
+        <v>7478027</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5849,13 +5849,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123699082</t>
+          <t>https://artportalen.se/Sighting/123699046</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123699083</v>
+        <v>123699082</v>
       </c>
       <c r="B52" t="n">
         <v>80367</v>
@@ -5890,10 +5890,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>855119</v>
+        <v>855140</v>
       </c>
       <c r="R52" t="n">
-        <v>7478027</v>
+        <v>7478068</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -5951,13 +5951,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123699083</t>
+          <t>https://artportalen.se/Sighting/123699082</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123699084</v>
+        <v>123699083</v>
       </c>
       <c r="B53" t="n">
         <v>80367</v>
@@ -5992,10 +5992,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>855181</v>
+        <v>855119</v>
       </c>
       <c r="R53" t="n">
-        <v>7478022</v>
+        <v>7478027</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6053,13 +6053,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123699084</t>
+          <t>https://artportalen.se/Sighting/123699083</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>124427403</v>
+        <v>123699084</v>
       </c>
       <c r="B54" t="n">
         <v>80367</v>
@@ -6090,17 +6090,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>854946</v>
+        <v>855181</v>
       </c>
       <c r="R54" t="n">
-        <v>7478367</v>
+        <v>7478022</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6124,12 +6124,12 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6138,7 +6138,6 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
@@ -6156,16 +6155,16 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427403</t>
+          <t>https://artportalen.se/Sighting/123699084</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>124855277</v>
+        <v>124427403</v>
       </c>
       <c r="B55" t="n">
-        <v>80461</v>
+        <v>80367</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6173,34 +6172,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6462</v>
+        <v>6457</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Dvärgtufs</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Scytinium teretiusculum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Wallr.) Otálora et al.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>855068</v>
+        <v>854946</v>
       </c>
       <c r="R55" t="n">
-        <v>7478046</v>
+        <v>7478367</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6227,12 +6226,12 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6241,6 +6240,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -6258,16 +6258,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855277</t>
+          <t>https://artportalen.se/Sighting/124427403</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123699089</v>
+        <v>124855277</v>
       </c>
       <c r="B56" t="n">
-        <v>80467</v>
+        <v>80461</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6275,37 +6275,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>855063</v>
+        <v>855068</v>
       </c>
       <c r="R56" t="n">
-        <v>7478073</v>
+        <v>7478046</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6329,12 +6329,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6360,13 +6360,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123699089</t>
+          <t>https://artportalen.se/Sighting/124855277</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123699090</v>
+        <v>123699089</v>
       </c>
       <c r="B57" t="n">
         <v>80467</v>
@@ -6401,10 +6401,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>854901</v>
+        <v>855063</v>
       </c>
       <c r="R57" t="n">
-        <v>7478143</v>
+        <v>7478073</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6462,13 +6462,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123699090</t>
+          <t>https://artportalen.se/Sighting/123699089</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>124427410</v>
+        <v>123699090</v>
       </c>
       <c r="B58" t="n">
         <v>80467</v>
@@ -6499,17 +6499,17 @@
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q58" t="n">
         <v>854901</v>
       </c>
       <c r="R58" t="n">
-        <v>7478310</v>
+        <v>7478143</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6564,13 +6564,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427410</t>
+          <t>https://artportalen.se/Sighting/123699090</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>124855512</v>
+        <v>124427410</v>
       </c>
       <c r="B59" t="n">
         <v>80467</v>
@@ -6601,14 +6601,14 @@
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>854911</v>
+        <v>854901</v>
       </c>
       <c r="R59" t="n">
-        <v>7478164</v>
+        <v>7478310</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6635,12 +6635,12 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6666,13 +6666,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855512</t>
+          <t>https://artportalen.se/Sighting/124427410</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>124855524</v>
+        <v>124855512</v>
       </c>
       <c r="B60" t="n">
         <v>80467</v>
@@ -6707,10 +6707,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>854793</v>
+        <v>854911</v>
       </c>
       <c r="R60" t="n">
-        <v>7477805</v>
+        <v>7478164</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6737,12 +6737,12 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6768,16 +6768,16 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855524</t>
+          <t>https://artportalen.se/Sighting/124855512</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123699048</v>
+        <v>124855524</v>
       </c>
       <c r="B61" t="n">
-        <v>80468</v>
+        <v>80467</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6785,37 +6785,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6464</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>855062</v>
+        <v>854793</v>
       </c>
       <c r="R61" t="n">
-        <v>7478067</v>
+        <v>7477805</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -6839,12 +6839,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6870,13 +6870,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123699048</t>
+          <t>https://artportalen.se/Sighting/124855524</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>123699049</v>
+        <v>123699048</v>
       </c>
       <c r="B62" t="n">
         <v>80468</v>
@@ -6911,10 +6911,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>855147</v>
+        <v>855062</v>
       </c>
       <c r="R62" t="n">
-        <v>7477980</v>
+        <v>7478067</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -6972,13 +6972,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123699049</t>
+          <t>https://artportalen.se/Sighting/123699048</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>123699050</v>
+        <v>123699049</v>
       </c>
       <c r="B63" t="n">
         <v>80468</v>
@@ -7013,10 +7013,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>855140</v>
+        <v>855147</v>
       </c>
       <c r="R63" t="n">
-        <v>7478022</v>
+        <v>7477980</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7074,13 +7074,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123699050</t>
+          <t>https://artportalen.se/Sighting/123699049</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>123699051</v>
+        <v>123699050</v>
       </c>
       <c r="B64" t="n">
         <v>80468</v>
@@ -7115,10 +7115,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>854961</v>
+        <v>855140</v>
       </c>
       <c r="R64" t="n">
-        <v>7478150</v>
+        <v>7478022</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7176,13 +7176,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123699051</t>
+          <t>https://artportalen.se/Sighting/123699050</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>124427345</v>
+        <v>123699051</v>
       </c>
       <c r="B65" t="n">
         <v>80468</v>
@@ -7213,17 +7213,17 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>854967</v>
+        <v>854961</v>
       </c>
       <c r="R65" t="n">
-        <v>7478177</v>
+        <v>7478150</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7247,12 +7247,12 @@
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7278,13 +7278,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427345</t>
+          <t>https://artportalen.se/Sighting/123699051</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>124427346</v>
+        <v>124427345</v>
       </c>
       <c r="B66" t="n">
         <v>80468</v>
@@ -7319,10 +7319,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>855044</v>
+        <v>854967</v>
       </c>
       <c r="R66" t="n">
-        <v>7478074</v>
+        <v>7478177</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7380,13 +7380,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427346</t>
+          <t>https://artportalen.se/Sighting/124427345</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>124427347</v>
+        <v>124427346</v>
       </c>
       <c r="B67" t="n">
         <v>80468</v>
@@ -7421,10 +7421,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>855063</v>
+        <v>855044</v>
       </c>
       <c r="R67" t="n">
-        <v>7478044</v>
+        <v>7478074</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7482,13 +7482,13 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427347</t>
+          <t>https://artportalen.se/Sighting/124427346</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>124427375</v>
+        <v>124427347</v>
       </c>
       <c r="B68" t="n">
         <v>80468</v>
@@ -7519,14 +7519,14 @@
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>854922</v>
+        <v>855063</v>
       </c>
       <c r="R68" t="n">
-        <v>7478323</v>
+        <v>7478044</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7567,24 +7567,8 @@
       <c r="AE68" t="b">
         <v>0</v>
       </c>
-      <c r="AF68" t="inlineStr"/>
       <c r="AG68" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ68" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK68" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO68" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
@@ -7600,13 +7584,13 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427375</t>
+          <t>https://artportalen.se/Sighting/124427347</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>124427380</v>
+        <v>124427375</v>
       </c>
       <c r="B69" t="n">
         <v>80468</v>
@@ -7641,10 +7625,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>854901</v>
+        <v>854922</v>
       </c>
       <c r="R69" t="n">
-        <v>7478310</v>
+        <v>7478323</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7685,8 +7669,24 @@
       <c r="AE69" t="b">
         <v>0</v>
       </c>
+      <c r="AF69" t="inlineStr"/>
       <c r="AG69" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ69" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK69" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO69" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
       </c>
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
@@ -7702,13 +7702,13 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427380</t>
+          <t>https://artportalen.se/Sighting/124427375</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>124855333</v>
+        <v>124427380</v>
       </c>
       <c r="B70" t="n">
         <v>80468</v>
@@ -7739,14 +7739,14 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>854924</v>
+        <v>854901</v>
       </c>
       <c r="R70" t="n">
-        <v>7478087</v>
+        <v>7478310</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7773,12 +7773,12 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7804,16 +7804,16 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855333</t>
+          <t>https://artportalen.se/Sighting/124427380</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>124855536</v>
+        <v>124855333</v>
       </c>
       <c r="B71" t="n">
-        <v>57950</v>
+        <v>80468</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7821,21 +7821,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100049</v>
+        <v>6464</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7845,10 +7845,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>854869</v>
+        <v>854924</v>
       </c>
       <c r="R71" t="n">
-        <v>7477778</v>
+        <v>7478087</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7875,17 +7875,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Bohål</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7911,33 +7906,33 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855536</t>
+          <t>https://artportalen.se/Sighting/124855333</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>124855257</v>
+        <v>124855536</v>
       </c>
       <c r="B72" t="n">
-        <v>57953</v>
+        <v>57950</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7952,10 +7947,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>854894</v>
+        <v>854869</v>
       </c>
       <c r="R72" t="n">
-        <v>7477768</v>
+        <v>7477778</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7992,7 +7987,7 @@
       </c>
       <c r="AC72" t="inlineStr">
         <is>
-          <t>Avbarkad klen död  gran.</t>
+          <t>Bohål</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8018,16 +8013,16 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855257</t>
+          <t>https://artportalen.se/Sighting/124855536</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>134119738</v>
+        <v>124855257</v>
       </c>
       <c r="B73" t="n">
-        <v>57975</v>
+        <v>57953</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8055,17 +8050,17 @@
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>855139</v>
+        <v>854894</v>
       </c>
       <c r="R73" t="n">
-        <v>7478131</v>
+        <v>7477768</v>
       </c>
       <c r="S73" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8089,17 +8084,17 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AC73" t="inlineStr">
         <is>
-          <t>Färska ringhack på tre granar stående nära varandra.</t>
+          <t>Avbarkad klen död  gran.</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8125,13 +8120,13 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119738</t>
+          <t>https://artportalen.se/Sighting/124855257</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>134119739</v>
+        <v>134119738</v>
       </c>
       <c r="B74" t="n">
         <v>57975</v>
@@ -8160,20 +8155,16 @@
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="K74" t="inlineStr"/>
-      <c r="L74" t="inlineStr"/>
-      <c r="M74" t="inlineStr"/>
-      <c r="N74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>854977</v>
+        <v>855139</v>
       </c>
       <c r="R74" t="n">
-        <v>7478284</v>
+        <v>7478131</v>
       </c>
       <c r="S74" t="n">
         <v>5</v>
@@ -8210,7 +8201,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall.</t>
+          <t>Färska ringhack på tre granar stående nära varandra.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8236,13 +8227,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119739</t>
+          <t>https://artportalen.se/Sighting/134119738</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>134119740</v>
+        <v>134119739</v>
       </c>
       <c r="B75" t="n">
         <v>57975</v>
@@ -8281,10 +8272,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>855183</v>
+        <v>854977</v>
       </c>
       <c r="R75" t="n">
-        <v>7478211</v>
+        <v>7478284</v>
       </c>
       <c r="S75" t="n">
         <v>5</v>
@@ -8321,7 +8312,7 @@
       </c>
       <c r="AC75" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran.</t>
+          <t>Färska ringhack på tall.</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8347,13 +8338,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119740</t>
+          <t>https://artportalen.se/Sighting/134119739</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>134119741</v>
+        <v>134119740</v>
       </c>
       <c r="B76" t="n">
         <v>57975</v>
@@ -8392,10 +8383,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>855170</v>
+        <v>855183</v>
       </c>
       <c r="R76" t="n">
-        <v>7478180</v>
+        <v>7478211</v>
       </c>
       <c r="S76" t="n">
         <v>5</v>
@@ -8458,13 +8449,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119741</t>
+          <t>https://artportalen.se/Sighting/134119740</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>134119742</v>
+        <v>134119741</v>
       </c>
       <c r="B77" t="n">
         <v>57975</v>
@@ -8503,10 +8494,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>855161</v>
+        <v>855170</v>
       </c>
       <c r="R77" t="n">
-        <v>7478173</v>
+        <v>7478180</v>
       </c>
       <c r="S77" t="n">
         <v>5</v>
@@ -8543,7 +8534,7 @@
       </c>
       <c r="AC77" t="inlineStr">
         <is>
-          <t>Färska ringhack på  gammal gran med cornflakesbark.</t>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8569,13 +8560,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119742</t>
+          <t>https://artportalen.se/Sighting/134119741</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>134119743</v>
+        <v>134119742</v>
       </c>
       <c r="B78" t="n">
         <v>57975</v>
@@ -8603,11 +8594,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
@@ -8618,10 +8605,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>855154</v>
+        <v>855161</v>
       </c>
       <c r="R78" t="n">
-        <v>7478157</v>
+        <v>7478173</v>
       </c>
       <c r="S78" t="n">
         <v>5</v>
@@ -8658,7 +8645,7 @@
       </c>
       <c r="AC78" t="inlineStr">
         <is>
-          <t>Färska ringhack på gran.</t>
+          <t>Färska ringhack på  gammal gran med cornflakesbark.</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8684,13 +8671,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119743</t>
+          <t>https://artportalen.se/Sighting/134119742</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>134119744</v>
+        <v>134119743</v>
       </c>
       <c r="B79" t="n">
         <v>57975</v>
@@ -8718,7 +8705,11 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I79" t="inlineStr"/>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K79" t="inlineStr"/>
       <c r="L79" t="inlineStr"/>
       <c r="M79" t="inlineStr"/>
@@ -8729,7 +8720,7 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>855156</v>
+        <v>855154</v>
       </c>
       <c r="R79" t="n">
         <v>7478157</v>
@@ -8795,13 +8786,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119744</t>
+          <t>https://artportalen.se/Sighting/134119743</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>134119745</v>
+        <v>134119744</v>
       </c>
       <c r="B80" t="n">
         <v>57975</v>
@@ -8840,10 +8831,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>855163</v>
+        <v>855156</v>
       </c>
       <c r="R80" t="n">
-        <v>7478143</v>
+        <v>7478157</v>
       </c>
       <c r="S80" t="n">
         <v>5</v>
@@ -8906,13 +8897,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119745</t>
+          <t>https://artportalen.se/Sighting/134119744</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>134119746</v>
+        <v>134119745</v>
       </c>
       <c r="B81" t="n">
         <v>57975</v>
@@ -8940,11 +8931,7 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
       <c r="M81" t="inlineStr"/>
@@ -8955,10 +8942,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>855151</v>
+        <v>855163</v>
       </c>
       <c r="R81" t="n">
-        <v>7478149</v>
+        <v>7478143</v>
       </c>
       <c r="S81" t="n">
         <v>5</v>
@@ -9021,38 +9008,38 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119746</t>
+          <t>https://artportalen.se/Sighting/134119745</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>134119752</v>
+        <v>134119746</v>
       </c>
       <c r="B82" t="n">
-        <v>57162</v>
+        <v>57975</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>100109</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
@@ -9060,16 +9047,20 @@
           <t>1</t>
         </is>
       </c>
+      <c r="K82" t="inlineStr"/>
+      <c r="L82" t="inlineStr"/>
+      <c r="M82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>855075</v>
+        <v>855151</v>
       </c>
       <c r="R82" t="n">
-        <v>7478048</v>
+        <v>7478149</v>
       </c>
       <c r="S82" t="n">
         <v>5</v>
@@ -9106,7 +9097,7 @@
       </c>
       <c r="AC82" t="inlineStr">
         <is>
-          <t>Uppflygande tupp.</t>
+          <t>Färska ringhack på gran.</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9132,16 +9123,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119752</t>
+          <t>https://artportalen.se/Sighting/134119746</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>123699041</v>
+        <v>134119752</v>
       </c>
       <c r="B83" t="n">
-        <v>57132</v>
+        <v>57162</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9149,37 +9140,41 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>102612</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>Torinen, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>854968</v>
+        <v>855075</v>
       </c>
       <c r="R83" t="n">
-        <v>7478151</v>
+        <v>7478048</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9203,17 +9198,17 @@
       </c>
       <c r="Y83" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
         <is>
-          <t>2025-04-01</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AC83" t="inlineStr">
         <is>
-          <t>Blindtarmstömning</t>
+          <t>Uppflygande tupp.</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9239,13 +9234,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123699041</t>
+          <t>https://artportalen.se/Sighting/134119752</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>123699058</v>
+        <v>123699041</v>
       </c>
       <c r="B84" t="n">
         <v>57132</v>
@@ -9280,10 +9275,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>855091</v>
+        <v>854968</v>
       </c>
       <c r="R84" t="n">
-        <v>7478072</v>
+        <v>7478151</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9320,7 +9315,7 @@
       </c>
       <c r="AC84" t="inlineStr">
         <is>
-          <t>Adult 1</t>
+          <t>Blindtarmstömning</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9346,13 +9341,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/123699058</t>
+          <t>https://artportalen.se/Sighting/123699041</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>124427393</v>
+        <v>123699058</v>
       </c>
       <c r="B85" t="n">
         <v>57132</v>
@@ -9383,17 +9378,17 @@
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Torinen, Nb</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>854990</v>
+        <v>855091</v>
       </c>
       <c r="R85" t="n">
-        <v>7478363</v>
+        <v>7478072</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9417,12 +9412,17 @@
       </c>
       <c r="Y85" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-01</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2025-04-01</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Adult 1</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9448,16 +9448,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427393</t>
+          <t>https://artportalen.se/Sighting/123699058</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>134119087</v>
+        <v>124427393</v>
       </c>
       <c r="B86" t="n">
-        <v>57165</v>
+        <v>57132</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9465,16 +9465,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>102613</v>
+        <v>102612</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9489,13 +9489,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>854821</v>
+        <v>854990</v>
       </c>
       <c r="R86" t="n">
-        <v>7477663</v>
+        <v>7478363</v>
       </c>
       <c r="S86" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9519,12 +9519,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9550,16 +9550,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119087</t>
+          <t>https://artportalen.se/Sighting/124427393</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>124855328</v>
+        <v>134119087</v>
       </c>
       <c r="B87" t="n">
-        <v>57144</v>
+        <v>57165</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9591,13 +9591,13 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>854802</v>
+        <v>854821</v>
       </c>
       <c r="R87" t="n">
-        <v>7477769</v>
+        <v>7477663</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9627,11 +9627,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Spillning</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9657,13 +9652,13 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855328</t>
+          <t>https://artportalen.se/Sighting/134119087</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>124855329</v>
+        <v>124855328</v>
       </c>
       <c r="B88" t="n">
         <v>57144</v>
@@ -9698,10 +9693,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>854676</v>
+        <v>854802</v>
       </c>
       <c r="R88" t="n">
-        <v>7477840</v>
+        <v>7477769</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9738,7 +9733,7 @@
       </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Spillning med blindtarmstömning-</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9764,16 +9759,16 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855329</t>
+          <t>https://artportalen.se/Sighting/124855328</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>134119082</v>
+        <v>124855329</v>
       </c>
       <c r="B89" t="n">
-        <v>58461</v>
+        <v>57144</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9781,21 +9776,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>103018</v>
+        <v>102613</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Orre</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Lyrurus tetrix</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9805,13 +9800,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>855075</v>
+        <v>854676</v>
       </c>
       <c r="R89" t="n">
-        <v>7478235</v>
+        <v>7477840</v>
       </c>
       <c r="S89" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9835,12 +9830,17 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Spillning med blindtarmstömning-</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -9866,38 +9866,38 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119082</t>
+          <t>https://artportalen.se/Sighting/124855329</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>124427369</v>
+        <v>134119082</v>
       </c>
       <c r="B90" t="n">
-        <v>58114</v>
+        <v>58461</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>103021</v>
+        <v>103018</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -9907,13 +9907,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>854943</v>
+        <v>855075</v>
       </c>
       <c r="R90" t="n">
-        <v>7478362</v>
+        <v>7478235</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -9937,12 +9937,12 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -9968,38 +9968,38 @@
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427369</t>
+          <t>https://artportalen.se/Sighting/134119082</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>134119723</v>
+        <v>124427369</v>
       </c>
       <c r="B91" t="n">
-        <v>58839</v>
+        <v>58114</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>208249</v>
+        <v>103021</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vanlig groda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Rana temporaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10009,13 +10009,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>854988</v>
+        <v>854943</v>
       </c>
       <c r="R91" t="n">
-        <v>7477812</v>
+        <v>7478362</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10039,12 +10039,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10070,16 +10070,16 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119723</t>
+          <t>https://artportalen.se/Sighting/124427369</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>134119924</v>
+        <v>134119723</v>
       </c>
       <c r="B92" t="n">
-        <v>108205</v>
+        <v>58839</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10087,21 +10087,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220083</v>
+        <v>208249</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Brudborste</t>
+          <t>Vanlig groda</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cirsium heterophyllum</t>
+          <t>Rana temporaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10111,10 +10111,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>855298</v>
+        <v>854988</v>
       </c>
       <c r="R92" t="n">
-        <v>7477963</v>
+        <v>7477812</v>
       </c>
       <c r="S92" t="n">
         <v>5</v>
@@ -10172,58 +10172,54 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119924</t>
+          <t>https://artportalen.se/Sighting/134119723</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>124427389</v>
+        <v>134119924</v>
       </c>
       <c r="B93" t="n">
-        <v>99118</v>
+        <v>108205</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>855110</v>
+        <v>855298</v>
       </c>
       <c r="R93" t="n">
-        <v>7478072</v>
+        <v>7477963</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10247,12 +10243,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10261,7 +10257,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10279,13 +10274,13 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427389</t>
+          <t>https://artportalen.se/Sighting/134119924</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124855355</v>
+        <v>124427389</v>
       </c>
       <c r="B94" t="n">
         <v>99118</v>
@@ -10313,17 +10308,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I94" t="inlineStr"/>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>854941</v>
+        <v>855110</v>
       </c>
       <c r="R94" t="n">
-        <v>7477803</v>
+        <v>7478072</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10350,17 +10349,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10387,13 +10381,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855355</t>
+          <t>https://artportalen.se/Sighting/124427389</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855356</v>
+        <v>124855355</v>
       </c>
       <c r="B95" t="n">
         <v>99118</v>
@@ -10428,10 +10422,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>855004</v>
+        <v>854941</v>
       </c>
       <c r="R95" t="n">
-        <v>7477822</v>
+        <v>7477803</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10495,13 +10489,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855356</t>
+          <t>https://artportalen.se/Sighting/124855355</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855357</v>
+        <v>124855356</v>
       </c>
       <c r="B96" t="n">
         <v>99118</v>
@@ -10529,21 +10523,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>855032</v>
+        <v>855004</v>
       </c>
       <c r="R96" t="n">
-        <v>7477845</v>
+        <v>7477822</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10607,13 +10597,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855357</t>
+          <t>https://artportalen.se/Sighting/124855356</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855358</v>
+        <v>124855357</v>
       </c>
       <c r="B97" t="n">
         <v>99118</v>
@@ -10641,17 +10631,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>854772</v>
+        <v>855032</v>
       </c>
       <c r="R97" t="n">
-        <v>7477881</v>
+        <v>7477845</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10715,13 +10709,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855358</t>
+          <t>https://artportalen.se/Sighting/124855357</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855359</v>
+        <v>124855358</v>
       </c>
       <c r="B98" t="n">
         <v>99118</v>
@@ -10756,10 +10750,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854838</v>
+        <v>854772</v>
       </c>
       <c r="R98" t="n">
-        <v>7477840</v>
+        <v>7477881</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10823,13 +10817,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855359</t>
+          <t>https://artportalen.se/Sighting/124855358</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855360</v>
+        <v>124855359</v>
       </c>
       <c r="B99" t="n">
         <v>99118</v>
@@ -10864,7 +10858,7 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854994</v>
+        <v>854838</v>
       </c>
       <c r="R99" t="n">
         <v>7477840</v>
@@ -10931,13 +10925,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855360</t>
+          <t>https://artportalen.se/Sighting/124855359</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855362</v>
+        <v>124855360</v>
       </c>
       <c r="B100" t="n">
         <v>99118</v>
@@ -10972,10 +10966,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854768</v>
+        <v>854994</v>
       </c>
       <c r="R100" t="n">
-        <v>7477866</v>
+        <v>7477840</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11039,13 +11033,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855362</t>
+          <t>https://artportalen.se/Sighting/124855360</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855364</v>
+        <v>124855362</v>
       </c>
       <c r="B101" t="n">
         <v>99118</v>
@@ -11080,10 +11074,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>855120</v>
+        <v>854768</v>
       </c>
       <c r="R101" t="n">
-        <v>7477887</v>
+        <v>7477866</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11147,13 +11141,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855364</t>
+          <t>https://artportalen.se/Sighting/124855362</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855365</v>
+        <v>124855364</v>
       </c>
       <c r="B102" t="n">
         <v>99118</v>
@@ -11188,10 +11182,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>854898</v>
+        <v>855120</v>
       </c>
       <c r="R102" t="n">
-        <v>7477806</v>
+        <v>7477887</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11255,13 +11249,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855365</t>
+          <t>https://artportalen.se/Sighting/124855364</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855367</v>
+        <v>124855365</v>
       </c>
       <c r="B103" t="n">
         <v>99118</v>
@@ -11289,21 +11283,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854723</v>
+        <v>854898</v>
       </c>
       <c r="R103" t="n">
-        <v>7477859</v>
+        <v>7477806</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11330,12 +11320,17 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11362,13 +11357,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855367</t>
+          <t>https://artportalen.se/Sighting/124855365</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855370</v>
+        <v>124855367</v>
       </c>
       <c r="B104" t="n">
         <v>99118</v>
@@ -11398,7 +11393,7 @@
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P104" t="inlineStr">
@@ -11407,10 +11402,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854788</v>
+        <v>854723</v>
       </c>
       <c r="R104" t="n">
-        <v>7477837</v>
+        <v>7477859</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11469,13 +11464,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855370</t>
+          <t>https://artportalen.se/Sighting/124855367</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855371</v>
+        <v>124855370</v>
       </c>
       <c r="B105" t="n">
         <v>99118</v>
@@ -11505,7 +11500,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>122</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11514,10 +11509,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854845</v>
+        <v>854788</v>
       </c>
       <c r="R105" t="n">
-        <v>7477869</v>
+        <v>7477837</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11544,12 +11539,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11576,13 +11571,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855371</t>
+          <t>https://artportalen.se/Sighting/124855370</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855373</v>
+        <v>124855371</v>
       </c>
       <c r="B106" t="n">
         <v>99118</v>
@@ -11612,7 +11607,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>112</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -11621,10 +11616,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854788</v>
+        <v>854845</v>
       </c>
       <c r="R106" t="n">
-        <v>7477850</v>
+        <v>7477869</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11651,12 +11646,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11683,13 +11678,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855373</t>
+          <t>https://artportalen.se/Sighting/124855371</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855377</v>
+        <v>124855373</v>
       </c>
       <c r="B107" t="n">
         <v>99118</v>
@@ -11719,19 +11714,19 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854672</v>
+        <v>854788</v>
       </c>
       <c r="R107" t="n">
-        <v>7477865</v>
+        <v>7477850</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11766,11 +11761,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
-        </is>
-      </c>
       <c r="AD107" t="b">
         <v>0</v>
       </c>
@@ -11795,13 +11785,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855377</t>
+          <t>https://artportalen.se/Sighting/124855373</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855390</v>
+        <v>124855377</v>
       </c>
       <c r="B108" t="n">
         <v>99118</v>
@@ -11831,19 +11821,19 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854899</v>
+        <v>854672</v>
       </c>
       <c r="R108" t="n">
-        <v>7477831</v>
+        <v>7477865</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11870,12 +11860,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -11902,13 +11897,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855390</t>
+          <t>https://artportalen.se/Sighting/124855377</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855392</v>
+        <v>124855390</v>
       </c>
       <c r="B109" t="n">
         <v>99118</v>
@@ -11938,7 +11933,7 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
@@ -11947,10 +11942,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854668</v>
+        <v>854899</v>
       </c>
       <c r="R109" t="n">
-        <v>7477874</v>
+        <v>7477831</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11977,12 +11972,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12009,13 +12004,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855392</t>
+          <t>https://artportalen.se/Sighting/124855390</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124855394</v>
+        <v>124855392</v>
       </c>
       <c r="B110" t="n">
         <v>99118</v>
@@ -12045,7 +12040,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12054,10 +12049,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>854897</v>
+        <v>854668</v>
       </c>
       <c r="R110" t="n">
-        <v>7477846</v>
+        <v>7477874</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12084,12 +12079,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12116,13 +12111,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855394</t>
+          <t>https://artportalen.se/Sighting/124855392</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124855395</v>
+        <v>124855394</v>
       </c>
       <c r="B111" t="n">
         <v>99118</v>
@@ -12152,7 +12147,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -12161,10 +12156,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>854745</v>
+        <v>854897</v>
       </c>
       <c r="R111" t="n">
-        <v>7477852</v>
+        <v>7477846</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12191,12 +12186,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12223,13 +12218,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855395</t>
+          <t>https://artportalen.se/Sighting/124855394</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124855398</v>
+        <v>124855395</v>
       </c>
       <c r="B112" t="n">
         <v>99118</v>
@@ -12259,19 +12254,19 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>854737</v>
+        <v>854745</v>
       </c>
       <c r="R112" t="n">
-        <v>7477850</v>
+        <v>7477852</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12306,11 +12301,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
-        </is>
-      </c>
       <c r="AD112" t="b">
         <v>0</v>
       </c>
@@ -12335,13 +12325,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855398</t>
+          <t>https://artportalen.se/Sighting/124855395</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124855401</v>
+        <v>124855398</v>
       </c>
       <c r="B113" t="n">
         <v>99118</v>
@@ -12371,19 +12361,19 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>854928</v>
+        <v>854737</v>
       </c>
       <c r="R113" t="n">
-        <v>7477769</v>
+        <v>7477850</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12418,6 +12408,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
+        </is>
+      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -12442,13 +12437,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855401</t>
+          <t>https://artportalen.se/Sighting/124855398</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124855404</v>
+        <v>124855401</v>
       </c>
       <c r="B114" t="n">
         <v>99118</v>
@@ -12478,7 +12473,7 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
@@ -12487,10 +12482,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>854832</v>
+        <v>854928</v>
       </c>
       <c r="R114" t="n">
-        <v>7477880</v>
+        <v>7477769</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12517,12 +12512,12 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12549,13 +12544,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855404</t>
+          <t>https://artportalen.se/Sighting/124855401</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124855407</v>
+        <v>124855404</v>
       </c>
       <c r="B115" t="n">
         <v>99118</v>
@@ -12583,17 +12578,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I115" t="inlineStr"/>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>854669</v>
+        <v>854832</v>
       </c>
       <c r="R115" t="n">
-        <v>7477869</v>
+        <v>7477880</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12620,17 +12619,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>3 kvm</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12657,13 +12651,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855407</t>
+          <t>https://artportalen.se/Sighting/124855404</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124855411</v>
+        <v>124855407</v>
       </c>
       <c r="B116" t="n">
         <v>99118</v>
@@ -12698,10 +12692,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>855100</v>
+        <v>854669</v>
       </c>
       <c r="R116" t="n">
-        <v>7477871</v>
+        <v>7477869</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12728,17 +12722,17 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>3 kvm</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12765,13 +12759,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855411</t>
+          <t>https://artportalen.se/Sighting/124855407</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124855415</v>
+        <v>124855411</v>
       </c>
       <c r="B117" t="n">
         <v>99118</v>
@@ -12806,10 +12800,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>854928</v>
+        <v>855100</v>
       </c>
       <c r="R117" t="n">
-        <v>7478107</v>
+        <v>7477871</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12844,12 +12838,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD117" t="b">
         <v>0</v>
       </c>
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -12867,13 +12867,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855415</t>
+          <t>https://artportalen.se/Sighting/124855411</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124855417</v>
+        <v>124855415</v>
       </c>
       <c r="B118" t="n">
         <v>99118</v>
@@ -12908,10 +12908,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>855202</v>
+        <v>854928</v>
       </c>
       <c r="R118" t="n">
-        <v>7477976</v>
+        <v>7478107</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12969,13 +12969,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855417</t>
+          <t>https://artportalen.se/Sighting/124855415</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124855418</v>
+        <v>124855417</v>
       </c>
       <c r="B119" t="n">
         <v>99118</v>
@@ -13010,10 +13010,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>855131</v>
+        <v>855202</v>
       </c>
       <c r="R119" t="n">
-        <v>7477924</v>
+        <v>7477976</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13071,13 +13071,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855418</t>
+          <t>https://artportalen.se/Sighting/124855417</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124855420</v>
+        <v>124855418</v>
       </c>
       <c r="B120" t="n">
         <v>99118</v>
@@ -13112,10 +13112,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>855071</v>
+        <v>855131</v>
       </c>
       <c r="R120" t="n">
-        <v>7477912</v>
+        <v>7477924</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13173,13 +13173,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855420</t>
+          <t>https://artportalen.se/Sighting/124855418</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124855421</v>
+        <v>124855420</v>
       </c>
       <c r="B121" t="n">
         <v>99118</v>
@@ -13214,10 +13214,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>854951</v>
+        <v>855071</v>
       </c>
       <c r="R121" t="n">
-        <v>7477899</v>
+        <v>7477912</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13275,13 +13275,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855421</t>
+          <t>https://artportalen.se/Sighting/124855420</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124855423</v>
+        <v>124855421</v>
       </c>
       <c r="B122" t="n">
         <v>99118</v>
@@ -13316,10 +13316,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>854915</v>
+        <v>854951</v>
       </c>
       <c r="R122" t="n">
-        <v>7477851</v>
+        <v>7477899</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13377,13 +13377,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855423</t>
+          <t>https://artportalen.se/Sighting/124855421</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124855425</v>
+        <v>124855423</v>
       </c>
       <c r="B123" t="n">
         <v>99118</v>
@@ -13418,10 +13418,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>855037</v>
+        <v>854915</v>
       </c>
       <c r="R123" t="n">
-        <v>7477854</v>
+        <v>7477851</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13479,13 +13479,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855425</t>
+          <t>https://artportalen.se/Sighting/124855423</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124855426</v>
+        <v>124855425</v>
       </c>
       <c r="B124" t="n">
         <v>99118</v>
@@ -13520,10 +13520,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>855070</v>
+        <v>855037</v>
       </c>
       <c r="R124" t="n">
-        <v>7477858</v>
+        <v>7477854</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13581,13 +13581,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855426</t>
+          <t>https://artportalen.se/Sighting/124855425</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124855427</v>
+        <v>124855426</v>
       </c>
       <c r="B125" t="n">
         <v>99118</v>
@@ -13622,10 +13622,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>854829</v>
+        <v>855070</v>
       </c>
       <c r="R125" t="n">
-        <v>7477821</v>
+        <v>7477858</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13683,13 +13683,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855427</t>
+          <t>https://artportalen.se/Sighting/124855426</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124855464</v>
+        <v>124855427</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -13724,10 +13724,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>854898</v>
+        <v>854829</v>
       </c>
       <c r="R126" t="n">
-        <v>7478156</v>
+        <v>7477821</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13785,13 +13785,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855464</t>
+          <t>https://artportalen.se/Sighting/124855427</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124855466</v>
+        <v>124855464</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -13826,10 +13826,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>854921</v>
+        <v>854898</v>
       </c>
       <c r="R127" t="n">
-        <v>7478082</v>
+        <v>7478156</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13887,13 +13887,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855466</t>
+          <t>https://artportalen.se/Sighting/124855464</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124855467</v>
+        <v>124855466</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -13928,10 +13928,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>855062</v>
+        <v>854921</v>
       </c>
       <c r="R128" t="n">
-        <v>7478002</v>
+        <v>7478082</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13989,13 +13989,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855467</t>
+          <t>https://artportalen.se/Sighting/124855466</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124855468</v>
+        <v>124855467</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -14030,10 +14030,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>855069</v>
+        <v>855062</v>
       </c>
       <c r="R129" t="n">
-        <v>7477999</v>
+        <v>7478002</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14091,16 +14091,16 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855468</t>
+          <t>https://artportalen.se/Sighting/124855467</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>134119832</v>
+        <v>124855468</v>
       </c>
       <c r="B130" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14128,17 +14128,17 @@
       <c r="I130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>854979</v>
+        <v>855069</v>
       </c>
       <c r="R130" t="n">
-        <v>7477885</v>
+        <v>7477999</v>
       </c>
       <c r="S130" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14162,17 +14162,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Ej återfunnet efter återbesök på tidigare fyndplats.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14181,7 +14176,6 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
@@ -14199,13 +14193,13 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119832</t>
+          <t>https://artportalen.se/Sighting/124855468</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134119088</v>
+        <v>134119832</v>
       </c>
       <c r="B131" t="n">
         <v>99195</v>
@@ -14233,21 +14227,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>854988</v>
+        <v>854979</v>
       </c>
       <c r="R131" t="n">
-        <v>7478320</v>
+        <v>7477885</v>
       </c>
       <c r="S131" t="n">
         <v>5</v>
@@ -14284,7 +14274,7 @@
       </c>
       <c r="AC131" t="inlineStr">
         <is>
-          <t>33 bladrosetter</t>
+          <t>Ej återfunnet efter återbesök på tidigare fyndplats.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14311,13 +14301,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119088</t>
+          <t>https://artportalen.se/Sighting/134119832</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134119830</v>
+        <v>134119088</v>
       </c>
       <c r="B132" t="n">
         <v>99195</v>
@@ -14345,17 +14335,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr"/>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>854795</v>
+        <v>854988</v>
       </c>
       <c r="R132" t="n">
-        <v>7477845</v>
+        <v>7478320</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -14392,7 +14386,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>Förekomsten i dåligt skick pga avverkning. Bladrosetter gulnade.</t>
+          <t>33 bladrosetter</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14419,13 +14413,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119830</t>
+          <t>https://artportalen.se/Sighting/134119088</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134119831</v>
+        <v>134119830</v>
       </c>
       <c r="B133" t="n">
         <v>99195</v>
@@ -14460,10 +14454,10 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>855070</v>
+        <v>854795</v>
       </c>
       <c r="R133" t="n">
-        <v>7478000</v>
+        <v>7477845</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14500,7 +14494,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Ej återfunnen på tidigare fyndplats pga avverkning.</t>
+          <t>Förekomsten i dåligt skick pga avverkning. Bladrosetter gulnade.</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14527,13 +14521,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119831</t>
+          <t>https://artportalen.se/Sighting/134119830</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134119833</v>
+        <v>134119831</v>
       </c>
       <c r="B134" t="n">
         <v>99195</v>
@@ -14568,10 +14562,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>854648</v>
+        <v>855070</v>
       </c>
       <c r="R134" t="n">
-        <v>7477883</v>
+        <v>7478000</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14606,12 +14600,18 @@
           <t>2026-06-03</t>
         </is>
       </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Ej återfunnen på tidigare fyndplats pga avverkning.</t>
+        </is>
+      </c>
       <c r="AD134" t="b">
         <v>0</v>
       </c>
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
@@ -14629,54 +14629,54 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119833</t>
+          <t>https://artportalen.se/Sighting/134119831</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>124855231</v>
+        <v>134119833</v>
       </c>
       <c r="B135" t="n">
-        <v>106229</v>
+        <v>99195</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>854954</v>
+        <v>854648</v>
       </c>
       <c r="R135" t="n">
-        <v>7478125</v>
+        <v>7477883</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14700,12 +14700,12 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14731,54 +14731,54 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855231</t>
+          <t>https://artportalen.se/Sighting/134119833</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>124855234</v>
+        <v>136866945</v>
       </c>
       <c r="B136" t="n">
-        <v>106229</v>
+        <v>99353</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>854727</v>
+        <v>855179</v>
       </c>
       <c r="R136" t="n">
-        <v>7477874</v>
+        <v>7478169</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -14802,12 +14802,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14833,13 +14833,13 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855234</t>
+          <t>https://artportalen.se/Sighting/136866945</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>124855240</v>
+        <v>124855231</v>
       </c>
       <c r="B137" t="n">
         <v>106229</v>
@@ -14874,10 +14874,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>854937</v>
+        <v>854954</v>
       </c>
       <c r="R137" t="n">
-        <v>7477782</v>
+        <v>7478125</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -14904,12 +14904,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14935,16 +14935,16 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855240</t>
+          <t>https://artportalen.se/Sighting/124855231</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>134119721</v>
+        <v>124855234</v>
       </c>
       <c r="B138" t="n">
-        <v>106309</v>
+        <v>106229</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -14972,17 +14972,17 @@
       <c r="I138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>854650</v>
+        <v>854727</v>
       </c>
       <c r="R138" t="n">
-        <v>7477883</v>
+        <v>7477874</v>
       </c>
       <c r="S138" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T138" t="inlineStr">
         <is>
@@ -15006,12 +15006,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15037,16 +15037,16 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119721</t>
+          <t>https://artportalen.se/Sighting/124855234</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>134119722</v>
+        <v>124855240</v>
       </c>
       <c r="B139" t="n">
-        <v>106309</v>
+        <v>106229</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15074,17 +15074,17 @@
       <c r="I139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>854940</v>
+        <v>854937</v>
       </c>
       <c r="R139" t="n">
-        <v>7477794</v>
+        <v>7477782</v>
       </c>
       <c r="S139" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T139" t="inlineStr">
         <is>
@@ -15108,12 +15108,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15139,16 +15139,16 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119722</t>
+          <t>https://artportalen.se/Sighting/124855240</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>124855316</v>
+        <v>134119721</v>
       </c>
       <c r="B140" t="n">
-        <v>97989</v>
+        <v>106309</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15156,37 +15156,37 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>855019</v>
+        <v>854650</v>
       </c>
       <c r="R140" t="n">
-        <v>7477888</v>
+        <v>7477883</v>
       </c>
       <c r="S140" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15210,12 +15210,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15241,16 +15241,16 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855316</t>
+          <t>https://artportalen.se/Sighting/134119721</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>134119085</v>
+        <v>134119722</v>
       </c>
       <c r="B141" t="n">
-        <v>99217</v>
+        <v>106309</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15258,21 +15258,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -15282,10 +15282,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>855063</v>
+        <v>854940</v>
       </c>
       <c r="R141" t="n">
-        <v>7478263</v>
+        <v>7477794</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15343,16 +15343,16 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119085</t>
+          <t>https://artportalen.se/Sighting/134119722</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>134119781</v>
+        <v>136866910</v>
       </c>
       <c r="B142" t="n">
-        <v>99217</v>
+        <v>106479</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15360,34 +15360,34 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>221952</v>
+        <v>221725</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>854643</v>
+        <v>855322</v>
       </c>
       <c r="R142" t="n">
-        <v>7477877</v>
+        <v>7478122</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15414,12 +15414,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15444,6 +15444,516 @@
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866910</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>136866911</v>
+      </c>
+      <c r="B143" t="n">
+        <v>106479</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>855203</v>
+      </c>
+      <c r="R143" t="n">
+        <v>7478220</v>
+      </c>
+      <c r="S143" t="n">
+        <v>5</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866911</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>136866912</v>
+      </c>
+      <c r="B144" t="n">
+        <v>106479</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>221725</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Ögonpyrola</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Moneses uniflora</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>(L.) A. Gray</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Lammivaara, Nb</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>855199</v>
+      </c>
+      <c r="R144" t="n">
+        <v>7478209</v>
+      </c>
+      <c r="S144" t="n">
+        <v>5</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136866912</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="n">
+        <v>124855316</v>
+      </c>
+      <c r="B145" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr"/>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>Vasikkavuoma, Nb</t>
+        </is>
+      </c>
+      <c r="Q145" t="n">
+        <v>855019</v>
+      </c>
+      <c r="R145" t="n">
+        <v>7477888</v>
+      </c>
+      <c r="S145" t="n">
+        <v>10</v>
+      </c>
+      <c r="T145" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AD145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG145" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT145" t="inlineStr"/>
+      <c r="AW145" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX145" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY145" t="inlineStr"/>
+      <c r="AZ145" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124855316</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="n">
+        <v>134119085</v>
+      </c>
+      <c r="B146" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr"/>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q146" t="n">
+        <v>855063</v>
+      </c>
+      <c r="R146" t="n">
+        <v>7478263</v>
+      </c>
+      <c r="S146" t="n">
+        <v>5</v>
+      </c>
+      <c r="T146" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U146" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V146" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W146" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y146" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA146" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG146" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT146" t="inlineStr"/>
+      <c r="AW146" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX146" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY146" t="inlineStr"/>
+      <c r="AZ146" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119085</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="n">
+        <v>134119781</v>
+      </c>
+      <c r="B147" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr"/>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q147" t="n">
+        <v>854643</v>
+      </c>
+      <c r="R147" t="n">
+        <v>7477877</v>
+      </c>
+      <c r="S147" t="n">
+        <v>5</v>
+      </c>
+      <c r="T147" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U147" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V147" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W147" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y147" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA147" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG147" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT147" t="inlineStr"/>
+      <c r="AW147" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX147" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY147" t="inlineStr"/>
+      <c r="AZ147" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134119781</t>
         </is>
@@ -15592,6 +16102,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ147"/>
+  <dimension ref="A1:AZ148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10280,52 +10280,48 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>124427389</v>
+        <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>99118</v>
+        <v>108378</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>220083</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Brudborste</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cirsium heterophyllum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
+          <t>(L.) Hill</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>855110</v>
+        <v>855299</v>
       </c>
       <c r="R94" t="n">
-        <v>7478072</v>
+        <v>7477978</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10349,12 +10345,17 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-04-24</t>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Område med högörtsvegetation.</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10363,7 +10364,6 @@
       <c r="AE94" t="b">
         <v>0</v>
       </c>
-      <c r="AF94" t="inlineStr"/>
       <c r="AG94" t="b">
         <v>0</v>
       </c>
@@ -10378,16 +10378,20 @@
           <t>Marie Karlsson</t>
         </is>
       </c>
-      <c r="AY94" t="inlineStr"/>
+      <c r="AY94" t="inlineStr">
+        <is>
+          <t>Projekt tretåig hackspett östra Norrbotten</t>
+        </is>
+      </c>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124427389</t>
+          <t>https://artportalen.se/Sighting/136866961</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>124855355</v>
+        <v>124427389</v>
       </c>
       <c r="B95" t="n">
         <v>99118</v>
@@ -10415,17 +10419,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>854941</v>
+        <v>855110</v>
       </c>
       <c r="R95" t="n">
-        <v>7477803</v>
+        <v>7478072</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10452,17 +10460,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>2025-04-24</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10489,13 +10492,13 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855355</t>
+          <t>https://artportalen.se/Sighting/124427389</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>124855356</v>
+        <v>124855355</v>
       </c>
       <c r="B96" t="n">
         <v>99118</v>
@@ -10530,10 +10533,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>855004</v>
+        <v>854941</v>
       </c>
       <c r="R96" t="n">
-        <v>7477822</v>
+        <v>7477803</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10597,13 +10600,13 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855356</t>
+          <t>https://artportalen.se/Sighting/124855355</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>124855357</v>
+        <v>124855356</v>
       </c>
       <c r="B97" t="n">
         <v>99118</v>
@@ -10631,21 +10634,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>855032</v>
+        <v>855004</v>
       </c>
       <c r="R97" t="n">
-        <v>7477845</v>
+        <v>7477822</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10709,13 +10708,13 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855357</t>
+          <t>https://artportalen.se/Sighting/124855356</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>124855358</v>
+        <v>124855357</v>
       </c>
       <c r="B98" t="n">
         <v>99118</v>
@@ -10743,17 +10742,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>854772</v>
+        <v>855032</v>
       </c>
       <c r="R98" t="n">
-        <v>7477881</v>
+        <v>7477845</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10817,13 +10820,13 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855358</t>
+          <t>https://artportalen.se/Sighting/124855357</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>124855359</v>
+        <v>124855358</v>
       </c>
       <c r="B99" t="n">
         <v>99118</v>
@@ -10858,10 +10861,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>854838</v>
+        <v>854772</v>
       </c>
       <c r="R99" t="n">
-        <v>7477840</v>
+        <v>7477881</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -10925,13 +10928,13 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855359</t>
+          <t>https://artportalen.se/Sighting/124855358</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>124855360</v>
+        <v>124855359</v>
       </c>
       <c r="B100" t="n">
         <v>99118</v>
@@ -10966,7 +10969,7 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>854994</v>
+        <v>854838</v>
       </c>
       <c r="R100" t="n">
         <v>7477840</v>
@@ -11033,13 +11036,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855360</t>
+          <t>https://artportalen.se/Sighting/124855359</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>124855362</v>
+        <v>124855360</v>
       </c>
       <c r="B101" t="n">
         <v>99118</v>
@@ -11074,10 +11077,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>854768</v>
+        <v>854994</v>
       </c>
       <c r="R101" t="n">
-        <v>7477866</v>
+        <v>7477840</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11141,13 +11144,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855362</t>
+          <t>https://artportalen.se/Sighting/124855360</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>124855364</v>
+        <v>124855362</v>
       </c>
       <c r="B102" t="n">
         <v>99118</v>
@@ -11182,10 +11185,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>855120</v>
+        <v>854768</v>
       </c>
       <c r="R102" t="n">
-        <v>7477887</v>
+        <v>7477866</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11249,13 +11252,13 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855364</t>
+          <t>https://artportalen.se/Sighting/124855362</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>124855365</v>
+        <v>124855364</v>
       </c>
       <c r="B103" t="n">
         <v>99118</v>
@@ -11290,10 +11293,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>854898</v>
+        <v>855120</v>
       </c>
       <c r="R103" t="n">
-        <v>7477806</v>
+        <v>7477887</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11357,13 +11360,13 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855365</t>
+          <t>https://artportalen.se/Sighting/124855364</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>124855367</v>
+        <v>124855365</v>
       </c>
       <c r="B104" t="n">
         <v>99118</v>
@@ -11391,21 +11394,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>854723</v>
+        <v>854898</v>
       </c>
       <c r="R104" t="n">
-        <v>7477859</v>
+        <v>7477806</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11432,12 +11431,17 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11464,13 +11468,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855367</t>
+          <t>https://artportalen.se/Sighting/124855365</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>124855370</v>
+        <v>124855367</v>
       </c>
       <c r="B105" t="n">
         <v>99118</v>
@@ -11500,7 +11504,7 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>122</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11509,10 +11513,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>854788</v>
+        <v>854723</v>
       </c>
       <c r="R105" t="n">
-        <v>7477837</v>
+        <v>7477859</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11571,13 +11575,13 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855370</t>
+          <t>https://artportalen.se/Sighting/124855367</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>124855371</v>
+        <v>124855370</v>
       </c>
       <c r="B106" t="n">
         <v>99118</v>
@@ -11607,7 +11611,7 @@
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>122</t>
         </is>
       </c>
       <c r="P106" t="inlineStr">
@@ -11616,10 +11620,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>854845</v>
+        <v>854788</v>
       </c>
       <c r="R106" t="n">
-        <v>7477869</v>
+        <v>7477837</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11646,12 +11650,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11678,13 +11682,13 @@
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855371</t>
+          <t>https://artportalen.se/Sighting/124855370</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>124855373</v>
+        <v>124855371</v>
       </c>
       <c r="B107" t="n">
         <v>99118</v>
@@ -11714,7 +11718,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>112</t>
         </is>
       </c>
       <c r="P107" t="inlineStr">
@@ -11723,10 +11727,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>854788</v>
+        <v>854845</v>
       </c>
       <c r="R107" t="n">
-        <v>7477850</v>
+        <v>7477869</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11753,12 +11757,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11785,13 +11789,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855373</t>
+          <t>https://artportalen.se/Sighting/124855371</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>124855377</v>
+        <v>124855373</v>
       </c>
       <c r="B108" t="n">
         <v>99118</v>
@@ -11821,19 +11825,19 @@
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>64</t>
+          <t>94</t>
         </is>
       </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>854672</v>
+        <v>854788</v>
       </c>
       <c r="R108" t="n">
-        <v>7477865</v>
+        <v>7477850</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11868,11 +11872,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC108" t="inlineStr">
-        <is>
-          <t>I utkanten av nytt hygge</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
@@ -11897,13 +11896,13 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855377</t>
+          <t>https://artportalen.se/Sighting/124855373</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>124855390</v>
+        <v>124855377</v>
       </c>
       <c r="B109" t="n">
         <v>99118</v>
@@ -11933,19 +11932,19 @@
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>64</t>
         </is>
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>854899</v>
+        <v>854672</v>
       </c>
       <c r="R109" t="n">
-        <v>7477831</v>
+        <v>7477865</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -11972,12 +11971,17 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>I utkanten av nytt hygge</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12004,13 +12008,13 @@
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855390</t>
+          <t>https://artportalen.se/Sighting/124855377</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>124855392</v>
+        <v>124855390</v>
       </c>
       <c r="B110" t="n">
         <v>99118</v>
@@ -12040,7 +12044,7 @@
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>28</t>
         </is>
       </c>
       <c r="P110" t="inlineStr">
@@ -12049,10 +12053,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>854668</v>
+        <v>854899</v>
       </c>
       <c r="R110" t="n">
-        <v>7477874</v>
+        <v>7477831</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12079,12 +12083,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12111,13 +12115,13 @@
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855392</t>
+          <t>https://artportalen.se/Sighting/124855390</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>124855394</v>
+        <v>124855392</v>
       </c>
       <c r="B111" t="n">
         <v>99118</v>
@@ -12147,7 +12151,7 @@
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>23</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -12156,10 +12160,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>854897</v>
+        <v>854668</v>
       </c>
       <c r="R111" t="n">
-        <v>7477846</v>
+        <v>7477874</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12186,12 +12190,12 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12218,13 +12222,13 @@
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855394</t>
+          <t>https://artportalen.se/Sighting/124855392</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>124855395</v>
+        <v>124855394</v>
       </c>
       <c r="B112" t="n">
         <v>99118</v>
@@ -12254,7 +12258,7 @@
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P112" t="inlineStr">
@@ -12263,10 +12267,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>854745</v>
+        <v>854897</v>
       </c>
       <c r="R112" t="n">
-        <v>7477852</v>
+        <v>7477846</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12293,12 +12297,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12325,13 +12329,13 @@
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855395</t>
+          <t>https://artportalen.se/Sighting/124855394</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>124855398</v>
+        <v>124855395</v>
       </c>
       <c r="B113" t="n">
         <v>99118</v>
@@ -12361,19 +12365,19 @@
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>17</t>
         </is>
       </c>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>854737</v>
+        <v>854745</v>
       </c>
       <c r="R113" t="n">
-        <v>7477850</v>
+        <v>7477852</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12408,11 +12412,6 @@
           <t>2025-05-06</t>
         </is>
       </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>I kanten av nytt hygge</t>
-        </is>
-      </c>
       <c r="AD113" t="b">
         <v>0</v>
       </c>
@@ -12437,13 +12436,13 @@
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855398</t>
+          <t>https://artportalen.se/Sighting/124855395</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>124855401</v>
+        <v>124855398</v>
       </c>
       <c r="B114" t="n">
         <v>99118</v>
@@ -12473,19 +12472,19 @@
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>13</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>854928</v>
+        <v>854737</v>
       </c>
       <c r="R114" t="n">
-        <v>7477769</v>
+        <v>7477850</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12520,6 +12519,11 @@
           <t>2025-05-06</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -12544,13 +12548,13 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855401</t>
+          <t>https://artportalen.se/Sighting/124855398</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>124855404</v>
+        <v>124855401</v>
       </c>
       <c r="B115" t="n">
         <v>99118</v>
@@ -12580,7 +12584,7 @@
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>13</t>
         </is>
       </c>
       <c r="P115" t="inlineStr">
@@ -12589,10 +12593,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>854832</v>
+        <v>854928</v>
       </c>
       <c r="R115" t="n">
-        <v>7477880</v>
+        <v>7477769</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12619,12 +12623,12 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12651,13 +12655,13 @@
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855404</t>
+          <t>https://artportalen.se/Sighting/124855401</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>124855407</v>
+        <v>124855404</v>
       </c>
       <c r="B116" t="n">
         <v>99118</v>
@@ -12685,17 +12689,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I116" t="inlineStr"/>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>854669</v>
+        <v>854832</v>
       </c>
       <c r="R116" t="n">
-        <v>7477869</v>
+        <v>7477880</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12722,17 +12730,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>3 kvm</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12759,13 +12762,13 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855407</t>
+          <t>https://artportalen.se/Sighting/124855404</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>124855411</v>
+        <v>124855407</v>
       </c>
       <c r="B117" t="n">
         <v>99118</v>
@@ -12800,10 +12803,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>855100</v>
+        <v>854669</v>
       </c>
       <c r="R117" t="n">
-        <v>7477871</v>
+        <v>7477869</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12830,17 +12833,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AC117" t="inlineStr">
         <is>
-          <t>I kanten av nytt hygge.</t>
+          <t>3 kvm</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12867,13 +12870,13 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855411</t>
+          <t>https://artportalen.se/Sighting/124855407</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>124855415</v>
+        <v>124855411</v>
       </c>
       <c r="B118" t="n">
         <v>99118</v>
@@ -12908,10 +12911,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>854928</v>
+        <v>855100</v>
       </c>
       <c r="R118" t="n">
-        <v>7478107</v>
+        <v>7477871</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -12946,12 +12949,18 @@
           <t>2025-05-07</t>
         </is>
       </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>I kanten av nytt hygge.</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
+      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
@@ -12969,13 +12978,13 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855415</t>
+          <t>https://artportalen.se/Sighting/124855411</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>124855417</v>
+        <v>124855415</v>
       </c>
       <c r="B119" t="n">
         <v>99118</v>
@@ -13010,10 +13019,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>855202</v>
+        <v>854928</v>
       </c>
       <c r="R119" t="n">
-        <v>7477976</v>
+        <v>7478107</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13071,13 +13080,13 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855417</t>
+          <t>https://artportalen.se/Sighting/124855415</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>124855418</v>
+        <v>124855417</v>
       </c>
       <c r="B120" t="n">
         <v>99118</v>
@@ -13112,10 +13121,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>855131</v>
+        <v>855202</v>
       </c>
       <c r="R120" t="n">
-        <v>7477924</v>
+        <v>7477976</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13173,13 +13182,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855418</t>
+          <t>https://artportalen.se/Sighting/124855417</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>124855420</v>
+        <v>124855418</v>
       </c>
       <c r="B121" t="n">
         <v>99118</v>
@@ -13214,10 +13223,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>855071</v>
+        <v>855131</v>
       </c>
       <c r="R121" t="n">
-        <v>7477912</v>
+        <v>7477924</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13275,13 +13284,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855420</t>
+          <t>https://artportalen.se/Sighting/124855418</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>124855421</v>
+        <v>124855420</v>
       </c>
       <c r="B122" t="n">
         <v>99118</v>
@@ -13316,10 +13325,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>854951</v>
+        <v>855071</v>
       </c>
       <c r="R122" t="n">
-        <v>7477899</v>
+        <v>7477912</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13377,13 +13386,13 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855421</t>
+          <t>https://artportalen.se/Sighting/124855420</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>124855423</v>
+        <v>124855421</v>
       </c>
       <c r="B123" t="n">
         <v>99118</v>
@@ -13418,10 +13427,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>854915</v>
+        <v>854951</v>
       </c>
       <c r="R123" t="n">
-        <v>7477851</v>
+        <v>7477899</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13479,13 +13488,13 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855423</t>
+          <t>https://artportalen.se/Sighting/124855421</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>124855425</v>
+        <v>124855423</v>
       </c>
       <c r="B124" t="n">
         <v>99118</v>
@@ -13520,10 +13529,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>855037</v>
+        <v>854915</v>
       </c>
       <c r="R124" t="n">
-        <v>7477854</v>
+        <v>7477851</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13581,13 +13590,13 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855425</t>
+          <t>https://artportalen.se/Sighting/124855423</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>124855426</v>
+        <v>124855425</v>
       </c>
       <c r="B125" t="n">
         <v>99118</v>
@@ -13622,10 +13631,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>855070</v>
+        <v>855037</v>
       </c>
       <c r="R125" t="n">
-        <v>7477858</v>
+        <v>7477854</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13683,13 +13692,13 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855426</t>
+          <t>https://artportalen.se/Sighting/124855425</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>124855427</v>
+        <v>124855426</v>
       </c>
       <c r="B126" t="n">
         <v>99118</v>
@@ -13724,10 +13733,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>854829</v>
+        <v>855070</v>
       </c>
       <c r="R126" t="n">
-        <v>7477821</v>
+        <v>7477858</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13785,13 +13794,13 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855427</t>
+          <t>https://artportalen.se/Sighting/124855426</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>124855464</v>
+        <v>124855427</v>
       </c>
       <c r="B127" t="n">
         <v>99118</v>
@@ -13826,10 +13835,10 @@
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>854898</v>
+        <v>854829</v>
       </c>
       <c r="R127" t="n">
-        <v>7478156</v>
+        <v>7477821</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13887,13 +13896,13 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855464</t>
+          <t>https://artportalen.se/Sighting/124855427</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>124855466</v>
+        <v>124855464</v>
       </c>
       <c r="B128" t="n">
         <v>99118</v>
@@ -13928,10 +13937,10 @@
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>854921</v>
+        <v>854898</v>
       </c>
       <c r="R128" t="n">
-        <v>7478082</v>
+        <v>7478156</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -13989,13 +13998,13 @@
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855466</t>
+          <t>https://artportalen.se/Sighting/124855464</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>124855467</v>
+        <v>124855466</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -14030,10 +14039,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>855062</v>
+        <v>854921</v>
       </c>
       <c r="R129" t="n">
-        <v>7478002</v>
+        <v>7478082</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14091,13 +14100,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855467</t>
+          <t>https://artportalen.se/Sighting/124855466</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>124855468</v>
+        <v>124855467</v>
       </c>
       <c r="B130" t="n">
         <v>99118</v>
@@ -14132,10 +14141,10 @@
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>855069</v>
+        <v>855062</v>
       </c>
       <c r="R130" t="n">
-        <v>7477999</v>
+        <v>7478002</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14193,16 +14202,16 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855468</t>
+          <t>https://artportalen.se/Sighting/124855467</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>134119832</v>
+        <v>124855468</v>
       </c>
       <c r="B131" t="n">
-        <v>99195</v>
+        <v>99118</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14230,17 +14239,17 @@
       <c r="I131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>854979</v>
+        <v>855069</v>
       </c>
       <c r="R131" t="n">
-        <v>7477885</v>
+        <v>7477999</v>
       </c>
       <c r="S131" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14264,17 +14273,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Ej återfunnet efter återbesök på tidigare fyndplats.</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14283,7 +14287,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -14301,13 +14304,13 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119832</t>
+          <t>https://artportalen.se/Sighting/124855468</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>134119088</v>
+        <v>134119832</v>
       </c>
       <c r="B132" t="n">
         <v>99195</v>
@@ -14335,21 +14338,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
+      <c r="I132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>854988</v>
+        <v>854979</v>
       </c>
       <c r="R132" t="n">
-        <v>7478320</v>
+        <v>7477885</v>
       </c>
       <c r="S132" t="n">
         <v>5</v>
@@ -14386,7 +14385,7 @@
       </c>
       <c r="AC132" t="inlineStr">
         <is>
-          <t>33 bladrosetter</t>
+          <t>Ej återfunnet efter återbesök på tidigare fyndplats.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14413,13 +14412,13 @@
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119088</t>
+          <t>https://artportalen.se/Sighting/134119832</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>134119830</v>
+        <v>134119088</v>
       </c>
       <c r="B133" t="n">
         <v>99195</v>
@@ -14447,17 +14446,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I133" t="inlineStr"/>
+      <c r="I133" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
       <c r="P133" t="inlineStr">
         <is>
           <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>854795</v>
+        <v>854988</v>
       </c>
       <c r="R133" t="n">
-        <v>7477845</v>
+        <v>7478320</v>
       </c>
       <c r="S133" t="n">
         <v>5</v>
@@ -14494,7 +14497,7 @@
       </c>
       <c r="AC133" t="inlineStr">
         <is>
-          <t>Förekomsten i dåligt skick pga avverkning. Bladrosetter gulnade.</t>
+          <t>33 bladrosetter</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14521,13 +14524,13 @@
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119830</t>
+          <t>https://artportalen.se/Sighting/134119088</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134119831</v>
+        <v>134119830</v>
       </c>
       <c r="B134" t="n">
         <v>99195</v>
@@ -14562,10 +14565,10 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>855070</v>
+        <v>854795</v>
       </c>
       <c r="R134" t="n">
-        <v>7478000</v>
+        <v>7477845</v>
       </c>
       <c r="S134" t="n">
         <v>5</v>
@@ -14602,7 +14605,7 @@
       </c>
       <c r="AC134" t="inlineStr">
         <is>
-          <t>Ej återfunnen på tidigare fyndplats pga avverkning.</t>
+          <t>Förekomsten i dåligt skick pga avverkning. Bladrosetter gulnade.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14629,13 +14632,13 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119831</t>
+          <t>https://artportalen.se/Sighting/134119830</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>134119833</v>
+        <v>134119831</v>
       </c>
       <c r="B135" t="n">
         <v>99195</v>
@@ -14670,10 +14673,10 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>854648</v>
+        <v>855070</v>
       </c>
       <c r="R135" t="n">
-        <v>7477883</v>
+        <v>7478000</v>
       </c>
       <c r="S135" t="n">
         <v>5</v>
@@ -14708,12 +14711,18 @@
           <t>2026-06-03</t>
         </is>
       </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Ej återfunnen på tidigare fyndplats pga avverkning.</t>
+        </is>
+      </c>
       <c r="AD135" t="b">
         <v>0</v>
       </c>
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
@@ -14731,16 +14740,16 @@
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119833</t>
+          <t>https://artportalen.se/Sighting/134119831</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>136866945</v>
+        <v>134119833</v>
       </c>
       <c r="B136" t="n">
-        <v>99353</v>
+        <v>99195</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -14768,14 +14777,14 @@
       <c r="I136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Lammivaara, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>855179</v>
+        <v>854648</v>
       </c>
       <c r="R136" t="n">
-        <v>7478169</v>
+        <v>7477883</v>
       </c>
       <c r="S136" t="n">
         <v>5</v>
@@ -14802,12 +14811,12 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14833,54 +14842,54 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866945</t>
+          <t>https://artportalen.se/Sighting/134119833</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>124855231</v>
+        <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>106229</v>
+        <v>99353</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>221725</v>
+        <v>220787</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Ögonpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Moneses uniflora</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(L.) A. Gray</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>854954</v>
+        <v>855179</v>
       </c>
       <c r="R137" t="n">
-        <v>7478125</v>
+        <v>7478169</v>
       </c>
       <c r="S137" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T137" t="inlineStr">
         <is>
@@ -14904,12 +14913,12 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -14935,13 +14944,13 @@
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855231</t>
+          <t>https://artportalen.se/Sighting/136866945</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>124855234</v>
+        <v>124855231</v>
       </c>
       <c r="B138" t="n">
         <v>106229</v>
@@ -14976,10 +14985,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>854727</v>
+        <v>854954</v>
       </c>
       <c r="R138" t="n">
-        <v>7477874</v>
+        <v>7478125</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15037,13 +15046,13 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855234</t>
+          <t>https://artportalen.se/Sighting/124855231</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>124855240</v>
+        <v>124855234</v>
       </c>
       <c r="B139" t="n">
         <v>106229</v>
@@ -15078,10 +15087,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>854937</v>
+        <v>854727</v>
       </c>
       <c r="R139" t="n">
-        <v>7477782</v>
+        <v>7477874</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15108,12 +15117,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-05-06</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15139,16 +15148,16 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855240</t>
+          <t>https://artportalen.se/Sighting/124855234</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>134119721</v>
+        <v>124855240</v>
       </c>
       <c r="B140" t="n">
-        <v>106309</v>
+        <v>106229</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15176,17 +15185,17 @@
       <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>854650</v>
+        <v>854937</v>
       </c>
       <c r="R140" t="n">
-        <v>7477883</v>
+        <v>7477782</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15210,12 +15219,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-06</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15241,13 +15250,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119721</t>
+          <t>https://artportalen.se/Sighting/124855240</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>134119722</v>
+        <v>134119721</v>
       </c>
       <c r="B141" t="n">
         <v>106309</v>
@@ -15282,10 +15291,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>854940</v>
+        <v>854650</v>
       </c>
       <c r="R141" t="n">
-        <v>7477794</v>
+        <v>7477883</v>
       </c>
       <c r="S141" t="n">
         <v>5</v>
@@ -15343,16 +15352,16 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119722</t>
+          <t>https://artportalen.se/Sighting/134119721</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>136866910</v>
+        <v>134119722</v>
       </c>
       <c r="B142" t="n">
-        <v>106479</v>
+        <v>106309</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -15380,14 +15389,14 @@
       <c r="I142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Lammivaara, Nb</t>
+          <t>Vasikkajoki, Nb</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>855322</v>
+        <v>854940</v>
       </c>
       <c r="R142" t="n">
-        <v>7478122</v>
+        <v>7477794</v>
       </c>
       <c r="S142" t="n">
         <v>5</v>
@@ -15414,12 +15423,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15445,13 +15454,13 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866910</t>
+          <t>https://artportalen.se/Sighting/134119722</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>136866911</v>
+        <v>136866910</v>
       </c>
       <c r="B143" t="n">
         <v>106479</v>
@@ -15486,10 +15495,10 @@
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>855203</v>
+        <v>855322</v>
       </c>
       <c r="R143" t="n">
-        <v>7478220</v>
+        <v>7478122</v>
       </c>
       <c r="S143" t="n">
         <v>5</v>
@@ -15547,13 +15556,13 @@
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866911</t>
+          <t>https://artportalen.se/Sighting/136866910</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>136866912</v>
+        <v>136866911</v>
       </c>
       <c r="B144" t="n">
         <v>106479</v>
@@ -15588,10 +15597,10 @@
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>855199</v>
+        <v>855203</v>
       </c>
       <c r="R144" t="n">
-        <v>7478209</v>
+        <v>7478220</v>
       </c>
       <c r="S144" t="n">
         <v>5</v>
@@ -15649,16 +15658,16 @@
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136866912</t>
+          <t>https://artportalen.se/Sighting/136866911</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>124855316</v>
+        <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>97989</v>
+        <v>106479</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -15666,37 +15675,37 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>221941</v>
+        <v>221725</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Ögonpyrola</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Moneses uniflora</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) A. Gray</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Vasikkavuoma, Nb</t>
+          <t>Lammivaara, Nb</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>855019</v>
+        <v>855199</v>
       </c>
       <c r="R145" t="n">
-        <v>7477888</v>
+        <v>7478209</v>
       </c>
       <c r="S145" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T145" t="inlineStr">
         <is>
@@ -15720,12 +15729,12 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2025-05-07</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -15751,16 +15760,16 @@
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/124855316</t>
+          <t>https://artportalen.se/Sighting/136866912</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>134119085</v>
+        <v>124855316</v>
       </c>
       <c r="B146" t="n">
-        <v>99217</v>
+        <v>97989</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -15768,37 +15777,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>221952</v>
+        <v>221941</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Vasikkajoki, Nb</t>
+          <t>Vasikkavuoma, Nb</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>855063</v>
+        <v>855019</v>
       </c>
       <c r="R146" t="n">
-        <v>7478263</v>
+        <v>7477888</v>
       </c>
       <c r="S146" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T146" t="inlineStr">
         <is>
@@ -15822,12 +15831,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-05-07</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -15853,13 +15862,13 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134119085</t>
+          <t>https://artportalen.se/Sighting/124855316</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>134119781</v>
+        <v>134119085</v>
       </c>
       <c r="B147" t="n">
         <v>99217</v>
@@ -15894,10 +15903,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>854643</v>
+        <v>855063</v>
       </c>
       <c r="R147" t="n">
-        <v>7477877</v>
+        <v>7478263</v>
       </c>
       <c r="S147" t="n">
         <v>5</v>
@@ -15954,6 +15963,108 @@
       </c>
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134119085</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="n">
+        <v>134119781</v>
+      </c>
+      <c r="B148" t="n">
+        <v>99217</v>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E148" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I148" t="inlineStr"/>
+      <c r="P148" t="inlineStr">
+        <is>
+          <t>Vasikkajoki, Nb</t>
+        </is>
+      </c>
+      <c r="Q148" t="n">
+        <v>854643</v>
+      </c>
+      <c r="R148" t="n">
+        <v>7477877</v>
+      </c>
+      <c r="S148" t="n">
+        <v>5</v>
+      </c>
+      <c r="T148" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U148" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V148" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W148" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="Y148" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AA148" t="inlineStr">
+        <is>
+          <t>2026-06-03</t>
+        </is>
+      </c>
+      <c r="AD148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG148" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT148" t="inlineStr"/>
+      <c r="AW148" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AX148" t="inlineStr">
+        <is>
+          <t>Marie Karlsson</t>
+        </is>
+      </c>
+      <c r="AY148" t="inlineStr"/>
+      <c r="AZ148" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/134119781</t>
         </is>
@@ -16107,6 +16218,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ145" r:id="rId144"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ146" r:id="rId145"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ147" r:id="rId146"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ148" r:id="rId147"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -1619,7 +1619,7 @@
         <v>136483159</v>
       </c>
       <c r="B11" t="n">
-        <v>101461</v>
+        <v>101467</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>136866951</v>
       </c>
       <c r="B47" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108378</v>
+        <v>108384</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106479</v>
+        <v>106485</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106479</v>
+        <v>106485</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106479</v>
+        <v>106485</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -1619,7 +1619,7 @@
         <v>136483159</v>
       </c>
       <c r="B11" t="n">
-        <v>101467</v>
+        <v>101469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>136866951</v>
       </c>
       <c r="B47" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108384</v>
+        <v>108386</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106485</v>
+        <v>106487</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106485</v>
+        <v>106487</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106485</v>
+        <v>106487</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -1619,7 +1619,7 @@
         <v>136483159</v>
       </c>
       <c r="B11" t="n">
-        <v>101469</v>
+        <v>101470</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>136866951</v>
       </c>
       <c r="B47" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108386</v>
+        <v>108387</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106487</v>
+        <v>106488</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106487</v>
+        <v>106488</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106487</v>
+        <v>106488</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -1619,7 +1619,7 @@
         <v>136483159</v>
       </c>
       <c r="B11" t="n">
-        <v>101470</v>
+        <v>101476</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108387</v>
+        <v>108393</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106488</v>
+        <v>106494</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106488</v>
+        <v>106494</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106488</v>
+        <v>106494</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -1619,7 +1619,7 @@
         <v>136483159</v>
       </c>
       <c r="B11" t="n">
-        <v>101476</v>
+        <v>101480</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -5342,7 +5342,7 @@
         <v>136866951</v>
       </c>
       <c r="B47" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108393</v>
+        <v>108397</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106494</v>
+        <v>106498</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106494</v>
+        <v>106498</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106494</v>
+        <v>106498</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108397</v>
+        <v>108399</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106498</v>
+        <v>106500</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106498</v>
+        <v>106500</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106498</v>
+        <v>106500</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -5342,7 +5342,7 @@
         <v>136866951</v>
       </c>
       <c r="B47" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108399</v>
+        <v>108401</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106500</v>
+        <v>106502</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -5342,7 +5342,7 @@
         <v>136866951</v>
       </c>
       <c r="B47" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108401</v>
+        <v>108414</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106502</v>
+        <v>106515</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106502</v>
+        <v>106515</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106502</v>
+        <v>106515</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -5342,7 +5342,7 @@
         <v>136866951</v>
       </c>
       <c r="B47" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108414</v>
+        <v>108416</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106515</v>
+        <v>106517</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108416</v>
+        <v>108421</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106517</v>
+        <v>106521</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106517</v>
+        <v>106521</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106517</v>
+        <v>106521</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -5342,7 +5342,7 @@
         <v>136866951</v>
       </c>
       <c r="B47" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108421</v>
+        <v>108442</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106521</v>
+        <v>106541</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106521</v>
+        <v>106541</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106521</v>
+        <v>106541</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108442</v>
+        <v>108443</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106541</v>
+        <v>106542</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106541</v>
+        <v>106542</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106541</v>
+        <v>106542</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -5342,7 +5342,7 @@
         <v>136866951</v>
       </c>
       <c r="B47" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108443</v>
+        <v>108448</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106542</v>
+        <v>106547</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106542</v>
+        <v>106547</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106542</v>
+        <v>106547</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108448</v>
+        <v>108451</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106547</v>
+        <v>106550</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106547</v>
+        <v>106550</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106547</v>
+        <v>106550</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -5342,7 +5342,7 @@
         <v>136866951</v>
       </c>
       <c r="B47" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108451</v>
+        <v>108457</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106550</v>
+        <v>106556</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106550</v>
+        <v>106556</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106550</v>
+        <v>106556</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108457</v>
+        <v>108458</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106556</v>
+        <v>106557</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -5342,7 +5342,7 @@
         <v>136866951</v>
       </c>
       <c r="B47" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108458</v>
+        <v>108470</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -14851,7 +14851,7 @@
         <v>136866945</v>
       </c>
       <c r="B137" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15463,7 +15463,7 @@
         <v>136866910</v>
       </c>
       <c r="B143" t="n">
-        <v>106557</v>
+        <v>106569</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>136866911</v>
       </c>
       <c r="B144" t="n">
-        <v>106557</v>
+        <v>106569</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -15667,7 +15667,7 @@
         <v>136866912</v>
       </c>
       <c r="B145" t="n">
-        <v>106557</v>
+        <v>106569</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108470</v>
+        <v>108471</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108471</v>
+        <v>108474</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -1619,7 +1619,7 @@
         <v>136483159</v>
       </c>
       <c r="B11" t="n">
-        <v>101480</v>
+        <v>101548</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 16006-2025 artfynd.xlsx
+++ b/artfynd/A 16006-2025 artfynd.xlsx
@@ -10283,7 +10283,7 @@
         <v>136866961</v>
       </c>
       <c r="B94" t="n">
-        <v>108474</v>
+        <v>108476</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
